--- a/tests/DB/Demo/JDemo.xlsx
+++ b/tests/DB/Demo/JDemo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArduinoProject\IO_Tester\tests\DB\MTC_AFT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArduinoProject\IO_Tester\tests\DB\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C4880D-8A1D-42DE-8F23-BF6DE18C8954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4FB29A-5C23-4DCF-8AD8-B55943A6408F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -634,7 +634,7 @@
         <v>22</v>
       </c>
       <c r="J2" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -672,7 +672,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -710,7 +710,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>17</v>
@@ -748,7 +748,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>17</v>
@@ -786,7 +786,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>17</v>
@@ -824,7 +824,7 @@
         <v>21</v>
       </c>
       <c r="J7" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>17</v>
@@ -862,7 +862,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>17</v>
@@ -900,7 +900,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>17</v>
@@ -938,7 +938,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>17</v>
@@ -976,7 +976,7 @@
         <v>22</v>
       </c>
       <c r="J11" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>17</v>
@@ -1014,7 +1014,7 @@
         <v>17</v>
       </c>
       <c r="J12" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>17</v>
@@ -1052,7 +1052,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>17</v>
@@ -1090,7 +1090,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>17</v>
@@ -1128,7 +1128,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>17</v>
@@ -1166,7 +1166,7 @@
         <v>21</v>
       </c>
       <c r="J16" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>17</v>
@@ -1204,7 +1204,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>17</v>
@@ -1242,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>17</v>
@@ -1280,7 +1280,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>17</v>
@@ -1318,7 +1318,7 @@
         <v>22</v>
       </c>
       <c r="J20" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>17</v>
@@ -1356,7 +1356,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>17</v>
@@ -1394,7 +1394,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>17</v>
@@ -1432,7 +1432,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>17</v>
@@ -1470,7 +1470,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>17</v>
@@ -1508,7 +1508,7 @@
         <v>21</v>
       </c>
       <c r="J25" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>17</v>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
       <c r="J26" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>17</v>
@@ -1584,7 +1584,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>17</v>
@@ -1622,7 +1622,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>17</v>
@@ -1660,7 +1660,7 @@
         <v>22</v>
       </c>
       <c r="J29" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>17</v>
@@ -1698,7 +1698,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>17</v>
@@ -1736,7 +1736,7 @@
         <v>17</v>
       </c>
       <c r="J31" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>17</v>
@@ -1774,7 +1774,7 @@
         <v>17</v>
       </c>
       <c r="J32" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>17</v>
@@ -1812,7 +1812,7 @@
         <v>17</v>
       </c>
       <c r="J33" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>17</v>
@@ -1850,7 +1850,7 @@
         <v>21</v>
       </c>
       <c r="J34" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>17</v>
@@ -1888,7 +1888,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>17</v>
@@ -1926,7 +1926,7 @@
         <v>17</v>
       </c>
       <c r="J36" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>17</v>
@@ -1964,7 +1964,7 @@
         <v>17</v>
       </c>
       <c r="J37" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>17</v>
@@ -2002,7 +2002,7 @@
         <v>22</v>
       </c>
       <c r="J38" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>17</v>
@@ -2040,7 +2040,7 @@
         <v>17</v>
       </c>
       <c r="J39" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>17</v>
@@ -2078,7 +2078,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>17</v>
@@ -2116,7 +2116,7 @@
         <v>17</v>
       </c>
       <c r="J41" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>17</v>
@@ -2154,7 +2154,7 @@
         <v>17</v>
       </c>
       <c r="J42" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>17</v>
@@ -2192,7 +2192,7 @@
         <v>21</v>
       </c>
       <c r="J43" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>17</v>
@@ -2230,7 +2230,7 @@
         <v>17</v>
       </c>
       <c r="J44" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>17</v>
@@ -2268,7 +2268,7 @@
         <v>17</v>
       </c>
       <c r="J45" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>17</v>
@@ -2306,7 +2306,7 @@
         <v>17</v>
       </c>
       <c r="J46" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>17</v>
@@ -2344,7 +2344,7 @@
         <v>22</v>
       </c>
       <c r="J47" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>17</v>
@@ -2382,7 +2382,7 @@
         <v>17</v>
       </c>
       <c r="J48" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>17</v>
@@ -2420,7 +2420,7 @@
         <v>17</v>
       </c>
       <c r="J49" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>17</v>
@@ -2458,7 +2458,7 @@
         <v>17</v>
       </c>
       <c r="J50" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>17</v>
@@ -2496,7 +2496,7 @@
         <v>17</v>
       </c>
       <c r="J51" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>17</v>
